--- a/src/assets/templates/workouts-import-template.xlsx
+++ b/src/assets/templates/workouts-import-template.xlsx
@@ -493,19 +493,14 @@
           <t>Upute za uvoz vježbi</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>Vježbe unosite u prvi list (Vjezbe), jedna vježba po retku, ispod zaglavlja.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -513,12 +508,8 @@
           <t>Ne mijenjajte nazive stupaca u zaglavlju.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -539,7 +530,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Naziv vježbe na hrvatskom (obavezno). Vježbe čiji naziv već postoji preskaču se.</t>
+          <t>Naziv vježbe na hrvatskom (obavezno).</t>
         </is>
       </c>
     </row>
@@ -551,7 +542,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Opis vježbe na hrvatskom.</t>
+          <t>Opis vježbe na hrvatskom. Vježbe s istim nazivom i opisom kao postojeće (ili ranije u datoteci) preskaču se kao duplikati.</t>
         </is>
       </c>
     </row>
@@ -580,7 +571,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
@@ -640,7 +630,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
@@ -651,7 +640,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Nazivi i opisi automatski se prevode na engleski i talijanski.</t>
+          <t>Nazivi i opisi automatski se prevode na engleski i talijanski. Uvoz radi u pozadini: sve ispravne vježbe se spremaju, a na email dobivate rezultat, popis vježbi koje nisu spremljene s razlogom te Excel datoteku s tim vježbama koju možete ispraviti i ponovno uvesti.</t>
         </is>
       </c>
     </row>

--- a/src/assets/templates/workouts-import-template.xlsx
+++ b/src/assets/templates/workouts-import-template.xlsx
@@ -438,13 +438,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,6 +467,11 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>WorkoutTypes</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Language</t>
         </is>
       </c>
     </row>
@@ -480,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -530,7 +536,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Naziv vježbe na hrvatskom (obavezno).</t>
+          <t>Naziv vježbe (obavezno), na jeziku iz stupca Language.</t>
         </is>
       </c>
     </row>
@@ -542,7 +548,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Opis vježbe na hrvatskom. Vježbe s istim nazivom i opisom kao postojeće (ili ranije u datoteci) preskaču se kao duplikati.</t>
+          <t>Opis vježbe, na jeziku iz stupca Language. Vježbe s istim nazivom i opisom kao postojeće (ili ranije u datoteci) preskaču se kao duplikati.</t>
         </is>
       </c>
     </row>
@@ -554,7 +560,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>YouTube poveznica videa (obavezno), npr. https://www.youtube.com/watch?v=IODxDxX7oi4</t>
+          <t>YouTube poveznica videa (neobavezno, može se dodati kasnije), npr. https://www.youtube.com/watch?v=IODxDxX7oi4</t>
         </is>
       </c>
     </row>
@@ -571,76 +577,100 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="4" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jezik teksta u retku: HR, EN ili IT (neobavezno, prazno = HR).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Primjer retka</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Čučanj</t>
-        </is>
-      </c>
+      <c r="B13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Osnovna vježba za noge i stražnjicu.</t>
+          <t>Čučanj</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VideoUrl</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aclHkVaku9U</t>
+          <t>Osnovna vježba za noge i stražnjicu.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>VideoUrl</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aclHkVaku9U</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>WorkoutTypes</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Snaga, Noge</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Napomena</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Nazivi i opisi automatski se prevode na engleski i talijanski. Uvoz radi u pozadini: sve ispravne vježbe se spremaju, a na email dobivate rezultat, popis vježbi koje nisu spremljene s razlogom te Excel datoteku s tim vježbama koju možete ispraviti i ponovno uvesti.</t>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Nazivi, opisi i nove vrste vježbi automatski se prevode s jezika retka na ostale jezike (HR, EN, IT). Uvoz radi u pozadini: sve ispravne vježbe se spremaju, a na email dobivate rezultat, popis vježbi koje nisu spremljene s razlogom te Excel datoteku s tim vježbama koju možete ispraviti i ponovno uvesti.</t>
         </is>
       </c>
     </row>
